--- a/stories/arbres/TREE-AUT-020.xlsx
+++ b/stories/arbres/TREE-AUT-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara écoute papa. Sara entend les mots : reprendre ses affaires, avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2590,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2759,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4123,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5487,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le vent est doux. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7039,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7206,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7205,6 +7399,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7369,6 +7568,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7735,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7902,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8069,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8236,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le vent est doux. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8403,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8570,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8529,6 +8763,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8693,6 +8932,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9099,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9266,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9433,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9600,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9767,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9934,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9853,6 +10127,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10296,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10463,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10630,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10797,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10964,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11131,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11298,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11484,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11848,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12015,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12208,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12377,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12544,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12711,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le vent est doux. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12878,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13045,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13212,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13379,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13572,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13741,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13908,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14075,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14242,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14409,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14576,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14743,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14936,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15105,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15272,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15439,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15606,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15773,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15940,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15586,6 +16036,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-020.xlsx
+++ b/stories/arbres/TREE-AUT-020.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara écoute papa. Sara entend les mots : reprendre ses affaires, avant de partir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Sara rejoint Tom. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Sara rejoint Léa. On entend un oiseau. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Sara rejoint Tom. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Sara rejoint Sami. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Sara rejoint Léa. Le vent est doux. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7211,6 +7250,7 @@
           <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7573,6 +7614,7 @@
           <t>narrateur|Sara rejoint Tom. On entend un oiseau. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7740,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7907,6 +7950,7 @@
           <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8074,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8241,6 +8286,7 @@
           <t>narrateur|Sara rejoint Sami. Le vent est doux. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8408,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8575,6 +8622,7 @@
           <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8937,6 +8986,7 @@
           <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9104,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9271,6 +9322,7 @@
           <t>narrateur|Sara rejoint Léa. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9438,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9605,6 +9658,7 @@
           <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9772,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9939,6 +9994,7 @@
           <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10190,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10358,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10694,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11030,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11304,6 +11367,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11491,6 +11555,7 @@
           <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11662,6 +11727,7 @@
           <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11853,6 +11919,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12020,6 +12087,7 @@
           <t>narrateur|Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12215,6 +12283,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12382,6 +12451,7 @@
           <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12549,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12716,6 +12787,7 @@
           <t>narrateur|Sara rejoint Léa. Le vent est doux. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12883,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13050,6 +13123,7 @@
           <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13217,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13384,6 +13459,7 @@
           <t>narrateur|Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13579,6 +13655,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13746,6 +13823,7 @@
           <t>narrateur|Sara rejoint Tom. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13913,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14080,6 +14159,7 @@
           <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14247,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14414,6 +14495,7 @@
           <t>narrateur|Sara rejoint Sami. Une feuille tombe. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14581,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14748,6 +14831,7 @@
           <t>narrateur|Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14943,6 +15027,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15110,6 +15195,7 @@
           <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15277,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15444,6 +15531,7 @@
           <t>narrateur|Sara rejoint Léa. Une feuille tombe. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15611,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15778,6 +15867,7 @@
           <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15945,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15963,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16043,6 +16134,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16244,6 +16349,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-020.xlsx
+++ b/stories/arbres/TREE-AUT-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retrouver ses affaires avant de partir — près de la fenêtre</t>
+          <t>Le chat à la fenêtre d'Amir</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un chat tapote la vitre. Amir joue près de la fenêtre, dans le carré de soleil. Avant de partir, il cherche le seau et le manteau, et il les prend.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara écoute papa. Sara entend les mots : reprendre ses affaires, avant de partir.</t>
+          <t>Un chat tapote la vitre. Sa queue fait tic, tic, tic. Le soleil entre, tout bas. Il fait un carré chaud sur le bois. Dans le carré, un seau jaune brille. Des grains de sable y dorment. Un manteau bleu est sur la chaise. Le manteau est à l'envers. Un doudou gris regarde par la fenêtre. Le doudou a une oreille pliée. L'air sent la poussière chaude. Amir, tu as vu le chat ? Oui, papa. Il tapote. Le soleil est déjà bas. C'est bientôt l'heure. En ce moment, Amir est près de la fenêtre. Il verse le sable du seau. Ça fait chh, tout doux. Ça fait chh, papa. Oui. Le sable chante. C'est l'heure de partir. On va reprendre ses affaires, avant de partir. Cherche le seau. Cherche le manteau. Puis on les prend. Amir regarde le seau jaune. Il est dans le carré de soleil. Je le vois. Bravo. On va les reprendre. Avant de partir. On sort un moment, d'accord. Le petit jardin est juste là. Puis on reprend tes affaires.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sara est avec papa, près de la fenêtre. Sara a envie de jouer. papa est là, tout près. On va apprendre : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara écoute papa. Sara entend les mots : reprendre ses affaires, avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un chat tapote la vitre.
+narrateur|Sa queue fait tic, tic, tic.
+narrateur|Le soleil entre, tout bas.
+narrateur|Il fait un carré chaud sur le bois.
+narrateur|Dans le carré, un seau jaune brille.
+narrateur|Des grains de sable y dorment.
+narrateur|Un manteau bleu est sur la chaise.
+narrateur|Le manteau est à l'envers.
+narrateur|Un doudou gris regarde par la fenêtre.
+narrateur|Le doudou a une oreille pliée.
+narrateur|L'air sent la poussière chaude.
+papa|Amir, tu as vu le chat ?
+enfant-m|Oui, papa.
+enfant-m|Il tapote.
+maman|Le soleil est déjà bas.
+maman|C'est bientôt l'heure.
+narrateur|En ce moment, Amir est près de la fenêtre.
+narrateur|Il verse le sable du seau.
+narrateur|Ça fait chh, tout doux.
+enfant-m|Ça fait chh, papa.
+papa|Oui. Le sable chante.
+papa|C'est l'heure de partir.
+papa|On va reprendre ses affaires, avant de partir.
+maman|Cherche le seau.
+maman|Cherche le manteau.
+maman|Puis on les prend.
+narrateur|Amir regarde le seau jaune.
+narrateur|Il est dans le carré de soleil.
+enfant-m|Je le vois.
+papa|Bravo.
+papa|On va les reprendre.
+papa|Avant de partir.
+maman|On sort un moment, d'accord.
+maman|Le petit jardin est juste là.
+papa|Puis on reprend tes affaires.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On joue où, avant de partir ? Le bac à sable. Le toboggan. Ou les balançoires.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,10 +1566,12 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>papa|On joue où, avant de partir ?
+narrateur|Le bac à sable.
+narrateur|Le toboggan.
+narrateur|Ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1549,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Amir va vers le bac à sable. Le bac est juste sous la fenêtre. Le sable est encore un peu frais. Le chat regarde depuis la vitre. On joue un peu. Puis on va reprendre ses affaires. Avant de partir. Cherche le seau, Amir. Amir cherche le seau. Le seau jaune est près du bac. Il le prend. J'ai le seau. Bravo. Tu as le seau. Le manteau aussi, tout à l'heure. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1736,23 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On écoute jusqu'au bout.
+          <t>narrateur|Amir va vers le bac à sable.
+narrateur|Le bac est juste sous la fenêtre.
+narrateur|Le sable est encore un peu frais.
+narrateur|Le chat regarde depuis la vitre.
+papa|On joue un peu.
+papa|Puis on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau, Amir.
+narrateur|Amir cherche le seau.
+narrateur|Le seau jaune est près du bac.
+narrateur|Il le prend.
+enfant-m|J'ai le seau.
+papa|Bravo. Tu as le seau.
+maman|Le manteau aussi, tout à l'heure.
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Avant de partir, que fait-on ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,10 +1937,9 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Avant de partir, que fait-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1906,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Cherche le seau et le manteau. Puis on les prend. J'ai le seau. Bravo, Amir. Le sable du bac reste au jardin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,10 +2108,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau et le manteau.
+maman|Puis on les prend.
+enfant-m|J'ai le seau.
+papa|Bravo, Amir.
+narrateur|Le sable du bac reste au jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2078,7 +2142,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu emportes quoi, en plus ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,10 +2306,12 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+          <t>maman|Tu emportes quoi, en plus ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2270,7 +2336,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+          <t>Amir a choisi le ballon. Le ballon est bleu, un peu lisse. Il roule une fois, puis s'arrête. Le sable du bac est encore frais. On prend le ballon. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le ballon reste près de papa.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,10 +2476,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le ballon.
+narrateur|Le ballon est bleu, un peu lisse.
+narrateur|Il roule une fois, puis s'arrête.
+narrateur|Le sable du bac est encore frais.
+papa|On prend le ballon.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le ballon reste près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2438,7 +2513,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2606,10 +2681,12 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2634,7 +2711,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Du sable est sur la manche du manteau. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le ballon bleu attend près de la chaise.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2774,10 +2851,23 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Du sable est sur la manche du manteau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le ballon bleu attend près de la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2802,7 +2892,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le ballon. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le ballon bleu attend près de la chaise. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2942,10 +3032,20 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le ballon bleu attend près de la chaise.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2970,7 +3070,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. On entend un oiseau. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Du sable est dans une chaussure. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Amir le verse, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3110,10 +3210,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Du sable est dans une chaussure.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Amir le verse, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3138,7 +3252,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le ballon. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Amir le verse, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3278,10 +3392,20 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Amir le verse, tout doux.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3306,7 +3430,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le ballon est contre la sangle du sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le sac bleu est un peu lourd.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3446,10 +3570,23 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le ballon est contre la sangle du sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le sac bleu est un peu lourd.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3474,7 +3611,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le ballon. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le sac bleu est un peu lourd. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3614,10 +3751,20 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le sac bleu est un peu lourd.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3642,7 +3789,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Amir a choisi le seau. Le seau est déjà dans ses mains. Il est jaune, un peu rêche. Le sable du bac est encore frais. Tu as cherché le seau. Tu l'as pris. C'est bien. Avant de partir. On va reprendre ses affaires. J'ai le seau. Bravo. Le manteau après. Le seau tapote contre sa jambe.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3782,10 +3929,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le seau.
+narrateur|Le seau est déjà dans ses mains.
+narrateur|Il est jaune, un peu rêche.
+narrateur|Le sable du bac est encore frais.
+papa|Tu as cherché le seau.
+papa|Tu l'as pris.
+maman|C'est bien. Avant de partir.
+maman|On va reprendre ses affaires.
+enfant-m|J'ai le seau.
+papa|Bravo. Le manteau après.
+narrateur|Le seau tapote contre sa jambe.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3810,7 +3966,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3978,10 +4134,12 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4006,7 +4164,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le seau tapote le manteau bleu. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Un grain de sable brille sur le tissu.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4146,10 +4304,23 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le seau tapote le manteau bleu.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Un grain de sable brille sur le tissu.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4174,7 +4345,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le seau. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Un grain de sable brille sur le tissu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4314,10 +4485,20 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le seau.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Un grain de sable brille sur le tissu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4342,7 +4523,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le seau est près des chaussures. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Les chaussures font toc toc.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4482,10 +4663,24 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le seau est près des chaussures.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Les chaussures font toc toc.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4510,7 +4705,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le seau. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Les chaussures font toc toc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4650,10 +4845,20 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le seau.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Les chaussures font toc toc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4678,7 +4883,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le seau entre dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Ça fait un petit bruit de plastique.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4818,10 +5023,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le seau entre dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Ça fait un petit bruit de plastique.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4846,7 +5064,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le seau. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Ça fait un petit bruit de plastique. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4986,10 +5204,20 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le seau.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Ça fait un petit bruit de plastique.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5014,7 +5242,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Amir a choisi le doudou. Le doudou gris a l'oreille pliée. Il est tout doux sous la main. Le sable du bac est encore frais. On prend le doudou. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le doudou reste contre Amir.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5154,10 +5382,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le doudou.
+narrateur|Le doudou gris a l'oreille pliée.
+narrateur|Il est tout doux sous la main.
+narrateur|Le sable du bac est encore frais.
+papa|On prend le doudou.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le doudou reste contre Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5182,7 +5419,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5350,10 +5587,12 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5378,7 +5617,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le doudou est dans le pli du manteau. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le manteau sent encore le soleil.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5518,10 +5757,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le doudou est dans le pli du manteau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le manteau sent encore le soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5546,7 +5798,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le doudou. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le manteau sent encore le soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5686,10 +5938,20 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le manteau sent encore le soleil.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5714,7 +5976,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le vent est doux. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le doudou est assis sur une chaussure. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. L'oreille pliée dépasse.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5854,10 +6116,24 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le vent est doux. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le doudou est assis sur une chaussure.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|L'oreille pliée dépasse.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5882,7 +6158,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le doudou. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. L'oreille pliée dépasse. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6022,10 +6298,20 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|L'oreille pliée dépasse.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6050,7 +6336,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. L'oreille du doudou est dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le sac est prêt, près de la fenêtre.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6190,10 +6476,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|L'oreille du doudou est dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le sac est prêt, près de la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6218,7 +6517,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au bac à sable. Il a pris le doudou. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le sac est prêt, près de la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6358,10 +6657,20 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au bac à sable.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le sac est prêt, près de la fenêtre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6386,7 +6695,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Amir va vers le toboggan. Le toboggan est dans le petit jardin. Le bois est froid, un peu. L'ombre de la fenêtre est dessus. On joue un peu. Puis on va reprendre ses affaires. Avant de partir. Cherche le seau, Amir. Amir cherche le seau. Le seau jaune est au pied du toboggan. Il le prend. J'ai le seau. Bravo. Tu as le seau. Le manteau aussi, tout à l'heure. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6526,11 +6835,23 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On attend son tour.
+          <t>narrateur|Amir va vers le toboggan.
+narrateur|Le toboggan est dans le petit jardin.
+narrateur|Le bois est froid, un peu.
+narrateur|L'ombre de la fenêtre est dessus.
+papa|On joue un peu.
+papa|Puis on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau, Amir.
+narrateur|Amir cherche le seau.
+narrateur|Le seau jaune est au pied du toboggan.
+narrateur|Il le prend.
+enfant-m|J'ai le seau.
+papa|Bravo. Tu as le seau.
+maman|Le manteau aussi, tout à l'heure.
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6555,7 +6876,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Avant de partir, que fait-on ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6715,10 +7036,9 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|Avant de partir, que fait-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6743,7 +7063,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Cherche le seau et le manteau. Puis on les prend. J'ai le seau. Bravo, Amir. Le bois du toboggan reste froid.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6887,10 +7207,16 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau et le manteau.
+maman|Puis on les prend.
+enfant-m|J'ai le seau.
+papa|Bravo, Amir.
+narrateur|Le bois du toboggan reste froid.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,7 +7241,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu emportes quoi, en plus ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7079,10 +7405,12 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>maman|Tu emportes quoi, en plus ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7107,7 +7435,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+          <t>Amir a choisi le ballon. Le ballon est bleu, un peu lisse. Il roule une fois, puis s'arrête. Le bois du toboggan est un peu froid. On prend le ballon. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le ballon reste près de papa.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7247,10 +7575,19 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le ballon.
+narrateur|Le ballon est bleu, un peu lisse.
+narrateur|Il roule une fois, puis s'arrête.
+narrateur|Le bois du toboggan est un peu froid.
+papa|On prend le ballon.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le ballon reste près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7275,7 +7612,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7443,10 +7780,12 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7471,7 +7810,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. On entend un oiseau. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le ballon a glissé sous le toboggan. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le manteau est chaud sur le bras.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7611,10 +7950,23 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le ballon a glissé sous le toboggan.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le manteau est chaud sur le bras.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7639,7 +7991,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le ballon. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le manteau est chaud sur le bras. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7779,10 +8131,20 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le manteau est chaud sur le bras.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7807,7 +8169,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le ballon est entre les deux chaussures. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le bois du toboggan est derrière.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7947,10 +8309,24 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le ballon est entre les deux chaussures.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le bois du toboggan est derrière.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7975,7 +8351,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le ballon. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le bois du toboggan est derrière. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8115,10 +8491,20 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le bois du toboggan est derrière.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8143,7 +8529,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le vent est doux. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le ballon roule jusqu'au sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le sac attend près de la porte.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8283,10 +8669,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le vent est doux. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le ballon roule jusqu'au sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le sac attend près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8311,7 +8710,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le ballon. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le sac attend près de la porte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8451,10 +8850,20 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le sac attend près de la porte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8479,7 +8888,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Amir a choisi le seau. Le seau est déjà dans ses mains. Il est jaune, un peu rêche. Le bois du toboggan est un peu froid. Tu as cherché le seau. Tu l'as pris. C'est bien. Avant de partir. On va reprendre ses affaires. J'ai le seau. Bravo. Le manteau après. Le seau tapote contre sa jambe.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8619,10 +9028,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le seau.
+narrateur|Le seau est déjà dans ses mains.
+narrateur|Il est jaune, un peu rêche.
+narrateur|Le bois du toboggan est un peu froid.
+papa|Tu as cherché le seau.
+papa|Tu l'as pris.
+maman|C'est bien. Avant de partir.
+maman|On va reprendre ses affaires.
+enfant-m|J'ai le seau.
+papa|Bravo. Le manteau après.
+narrateur|Le seau tapote contre sa jambe.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8647,7 +9065,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8815,10 +9233,12 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8843,7 +9263,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le seau est contre le manteau. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le toboggan reste dans le jardin.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8983,10 +9403,23 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le seau est contre le manteau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le toboggan reste dans le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9011,7 +9444,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le seau. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le toboggan reste dans le jardin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9151,10 +9584,20 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le seau.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le toboggan reste dans le jardin.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9179,7 +9622,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Une goutte d'eau tombe du seau. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Elle s'arrête près d'une chaussure.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9319,10 +9762,24 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Une goutte d'eau tombe du seau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Elle s'arrête près d'une chaussure.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9347,7 +9804,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le seau. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Elle s'arrête près d'une chaussure. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9487,10 +9944,20 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le seau.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Elle s'arrête près d'une chaussure.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9515,7 +9982,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le seau est dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le sac bleu tient bien.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9655,10 +10122,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le seau est dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le sac bleu tient bien.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9683,7 +10163,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le seau. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le sac bleu tient bien. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9823,10 +10303,20 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le seau.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le sac bleu tient bien.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9851,7 +10341,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Amir a choisi le doudou. Le doudou gris a l'oreille pliée. Il est tout doux sous la main. Le bois du toboggan est un peu froid. On prend le doudou. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le doudou reste contre Amir.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9991,10 +10481,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le doudou.
+narrateur|Le doudou gris a l'oreille pliée.
+narrateur|Il est tout doux sous la main.
+narrateur|Le bois du toboggan est un peu froid.
+papa|On prend le doudou.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le doudou reste contre Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10019,7 +10518,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10187,10 +10686,12 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10215,7 +10716,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le vent est doux. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le doudou a voyagé sur le toboggan. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Il est maintenant dans le manteau.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10355,10 +10856,23 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le vent est doux. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le doudou a voyagé sur le toboggan.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Il est maintenant dans le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10383,7 +10897,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le doudou. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Il est maintenant dans le manteau. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10523,10 +11037,20 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Il est maintenant dans le manteau.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10551,7 +11075,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le doudou est sur une chaussure. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le toboggan est vide, maintenant.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10691,10 +11215,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le doudou est sur une chaussure.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le toboggan est vide, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10719,7 +11257,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le doudou. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le toboggan est vide, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10859,10 +11397,20 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le toboggan est vide, maintenant.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10887,7 +11435,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Une feuille tombe. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le doudou entre dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le sac sent encore le bois.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11027,10 +11575,23 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le doudou entre dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le sac sent encore le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11055,7 +11616,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué au toboggan. Il a pris le doudou. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le sac sent encore le bois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11195,10 +11756,20 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué au toboggan.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le sac sent encore le bois.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11223,7 +11794,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Amir va vers les balançoires. Les cordes bougent un peu. Le siège de bois est lisse. Le chat tapote encore la vitre. On joue un peu. Puis on va reprendre ses affaires. Avant de partir. Cherche le seau, Amir. Amir cherche le seau. Le seau jaune est sous la balançoire. Il le prend. J'ai le seau. Bravo. Tu as le seau. Le manteau aussi, tout à l'heure. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11363,11 +11934,23 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : reprendre ses affaires, avant de partir. Voici le geste : chercher seau et manteau ; les prendre. On montre du doigt, sans courir.
+          <t>narrateur|Amir va vers les balançoires.
+narrateur|Les cordes bougent un peu.
+narrateur|Le siège de bois est lisse.
+narrateur|Le chat tapote encore la vitre.
+papa|On joue un peu.
+papa|Puis on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau, Amir.
+narrateur|Amir cherche le seau.
+narrateur|Le seau jaune est sous la balançoire.
+narrateur|Il le prend.
+enfant-m|J'ai le seau.
+papa|Bravo. Tu as le seau.
+maman|Le manteau aussi, tout à l'heure.
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11392,7 +11975,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Retrouver ses affaires avant de partir.</t>
+          <t>Avant de partir, que fait-on ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,10 +12135,9 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Retrouver ses affaires avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Avant de partir, que fait-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11580,7 +12162,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
+          <t>Oui. On va reprendre ses affaires. Avant de partir. Cherche le seau et le manteau. Puis on les prend. J'ai le seau. Bravo, Amir. La corde de la balançoire se tait.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,10 +12306,16 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : chercher seau et manteau ; les prendre. Sara respire. Sara retient : reprendre ses affaires, avant de partir. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Oui.
+papa|On va reprendre ses affaires.
+papa|Avant de partir.
+maman|Cherche le seau et le manteau.
+maman|Puis on les prend.
+enfant-m|J'ai le seau.
+papa|Bravo, Amir.
+narrateur|La corde de la balançoire se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11752,7 +12340,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Tu emportes quoi, en plus ? Le ballon. Le seau. Ou le doudou.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11916,10 +12504,12 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+          <t>maman|Tu emportes quoi, en plus ?
+narrateur|Le ballon.
+narrateur|Le seau.
+narrateur|Ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11944,7 +12534,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
+          <t>Amir a choisi le ballon. Le ballon est bleu, un peu lisse. Il roule une fois, puis s'arrête. La corde de la balançoire fait criiic. On prend le ballon. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le ballon reste près de papa.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12084,10 +12674,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On rit un peu. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le ballon.
+narrateur|Le ballon est bleu, un peu lisse.
+narrateur|Il roule une fois, puis s'arrête.
+narrateur|La corde de la balançoire fait criiic.
+papa|On prend le ballon.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le ballon reste près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12112,7 +12711,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12280,10 +12879,12 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12308,7 +12909,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. L'ombre de la balançoire est sur le manteau. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le ballon est calme, à côté.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12448,10 +13049,23 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Ça sent le pain chaud. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|L'ombre de la balançoire est sur le manteau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le ballon est calme, à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12476,7 +13090,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le ballon. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le ballon est calme, à côté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12616,10 +13230,20 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le ballon est calme, à côté.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12644,7 +13268,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le vent est doux. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le ballon est près des chaussures. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. La corde de la balançoire se tait.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12784,10 +13408,24 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le vent est doux. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le ballon est près des chaussures.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|La corde de la balançoire se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12812,7 +13450,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le ballon. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. La corde de la balançoire se tait. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12952,10 +13590,20 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|La corde de la balançoire se tait.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12980,7 +13628,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le sol est un peu froid. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le ballon tapote le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le chat n'est plus à la vitre.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13120,10 +13768,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le sol est un peu froid. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le ballon tapote le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le chat n'est plus à la vitre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13148,7 +13809,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le ballon. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le chat n'est plus à la vitre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13288,10 +13949,20 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le ballon.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le chat n'est plus à la vitre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13316,7 +13987,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
+          <t>Amir a choisi le seau. Le seau est déjà dans ses mains. Il est jaune, un peu rêche. La corde de la balançoire fait criiic. Tu as cherché le seau. Tu l'as pris. C'est bien. Avant de partir. On va reprendre ses affaires. J'ai le seau. Bravo. Le manteau après. Le seau tapote contre sa jambe.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13456,10 +14127,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tait une seconde. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le seau.
+narrateur|Le seau est déjà dans ses mains.
+narrateur|Il est jaune, un peu rêche.
+narrateur|La corde de la balançoire fait criiic.
+papa|Tu as cherché le seau.
+papa|Tu l'as pris.
+maman|C'est bien. Avant de partir.
+maman|On va reprendre ses affaires.
+enfant-m|J'ai le seau.
+papa|Bravo. Le manteau après.
+narrateur|Le seau tapote contre sa jambe.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13484,7 +14164,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13652,10 +14332,12 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13680,7 +14362,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le seau est sous le bras, avec le manteau. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Une feuille tourne près de la balançoire.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13820,10 +14502,23 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le vent est doux. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le seau est sous le bras, avec le manteau.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Une feuille tourne près de la balançoire.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13848,7 +14543,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le seau. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Une feuille tourne près de la balançoire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13988,10 +14683,20 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le seau.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Une feuille tourne près de la balançoire.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14016,7 +14721,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le seau est entre les chaussures. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Les lacets font un petit bruit.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14156,10 +14861,24 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Le sol est un peu froid. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le seau est entre les chaussures.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Les lacets font un petit bruit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14184,7 +14903,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le seau. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Les lacets font un petit bruit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14324,10 +15043,20 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le seau.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Les lacets font un petit bruit.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14352,7 +15081,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Une feuille tombe. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le seau est dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. La balançoire ne bouge plus.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14492,10 +15221,23 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Une feuille tombe. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le seau est dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|La balançoire ne bouge plus.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14520,7 +15262,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le seau. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. La balançoire ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14660,10 +15402,20 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le seau.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|La balançoire ne bouge plus.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14688,7 +15440,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
+          <t>Amir a choisi le doudou. Le doudou gris a l'oreille pliée. Il est tout doux sous la main. La corde de la balançoire fait criiic. On prend le doudou. Et on va reprendre ses affaires. Avant de partir. Tu as le seau ? Oui. Il est jaune. Bravo. Le manteau après. Le doudou reste contre Amir.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14828,10 +15580,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : chercher seau et manteau ; les prendre. Sara répète tout bas : reprendre ses affaires, avant de partir. On se tient la main. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Amir a choisi le doudou.
+narrateur|Le doudou gris a l'oreille pliée.
+narrateur|Il est tout doux sous la main.
+narrateur|La corde de la balançoire fait criiic.
+papa|On prend le doudou.
+papa|Et on va reprendre ses affaires.
+papa|Avant de partir.
+maman|Tu as le seau ?
+enfant-m|Oui. Il est jaune.
+papa|Bravo. Le manteau après.
+narrateur|Le doudou reste contre Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14856,7 +15617,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Il reste quoi, avant de partir ? Le manteau. Les chaussures. Ou le sac.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15024,10 +15785,12 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+          <t>papa|Il reste quoi, avant de partir ?
+narrateur|Le manteau.
+narrateur|Les chaussures.
+narrateur|Ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15052,7 +15815,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le manteau. Le manteau bleu est sur la chaise. Il est encore à l'envers. Le doudou est dans le manteau bleu. Avant de partir, on va reprendre ses affaires. Prends le manteau, Amir. Amir prend le manteau. Le tissu est un peu rêche. Je l'ai, papa. Bravo. Tu as le manteau. Et le seau aussi. Tu as repris tes affaires. Avant de partir. C'est du bon travail. La corde fait un dernier criiic.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15192,10 +15955,23 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Le sol est un peu froid. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Amir cherche le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Il est encore à l'envers.
+narrateur|Le doudou est dans le manteau bleu.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Prends le manteau, Amir.
+narrateur|Amir prend le manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-m|Je l'ai, papa.
+papa|Bravo. Tu as le manteau.
+papa|Et le seau aussi.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|La corde fait un dernier criiic.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15220,7 +15996,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le doudou. Puis il a pris le manteau. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. La corde fait un dernier criiic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15360,10 +16136,20 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a pris le manteau.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|La corde fait un dernier criiic.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15388,7 +16174,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Une feuille tombe. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche les chaussures. Elles sont près de la porte. Le manteau bleu attend encore. Le doudou est sur les chaussures. Avant de partir, on va reprendre ses affaires. Les chaussures, puis le manteau. Amir met les chaussures. Les lacets font un petit bruit. Puis il prend le manteau. J'ai le manteau. Bravo. Tu as le seau. Tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le chat a quitté la vitre.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15528,10 +16314,24 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Une feuille tombe. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Amir cherche les chaussures.
+narrateur|Elles sont près de la porte.
+narrateur|Le manteau bleu attend encore.
+narrateur|Le doudou est sur les chaussures.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Les chaussures, puis le manteau.
+narrateur|Amir met les chaussures.
+narrateur|Les lacets font un petit bruit.
+narrateur|Puis il prend le manteau.
+enfant-m|J'ai le manteau.
+papa|Bravo. Tu as le seau.
+papa|Tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le chat a quitté la vitre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,7 +16356,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le doudou. Puis il a mis les chaussures. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le chat a quitté la vitre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15696,10 +16496,20 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a mis les chaussures.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le chat a quitté la vitre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15724,7 +16534,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. L'eau coule, tout petit bruit. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
+          <t>Amir cherche le sac. Le sac bleu est près de la fenêtre. Les sangles pendent, molles. Le doudou est dans le sac. Avant de partir, on va reprendre ses affaires. Le seau dans le sac, comme j'ai dit. Amir met le seau dans le sac. Puis il prend le manteau. Le seau est dans le sac. Bravo. Tu as mis ce que maman a dit. Et tu as le manteau. Tu as repris tes affaires. Avant de partir. C'est du bon travail. Le carré de soleil est vide, maintenant.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15864,10 +16674,23 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. L'eau coule, tout petit bruit. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Retrouver ses affaires avant de partir. Voici le geste : chercher seau et manteau ; les prendre. Sara a entendu : reprendre ses affaires, avant de partir. Sara dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Amir cherche le sac.
+narrateur|Le sac bleu est près de la fenêtre.
+narrateur|Les sangles pendent, molles.
+narrateur|Le doudou est dans le sac.
+papa|Avant de partir, on va reprendre ses affaires.
+maman|Le seau dans le sac, comme j'ai dit.
+narrateur|Amir met le seau dans le sac.
+narrateur|Puis il prend le manteau.
+enfant-m|Le seau est dans le sac.
+papa|Bravo. Tu as mis ce que maman a dit.
+papa|Et tu as le manteau.
+maman|Tu as repris tes affaires.
+maman|Avant de partir.
+papa|C'est du bon travail.
+narrateur|Le carré de soleil est vide, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15892,7 +16715,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir était près de la fenêtre. Il a joué aux balançoires. Il a pris le doudou. Puis il a préparé le sac. Il a repris ses affaires. Avant de partir. Bravo, Amir. Tu as fait du bon travail. J'ai le seau. J'ai le manteau. Le carré de soleil est vide, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16032,10 +16855,20 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr"/>
+          <t>narrateur|Amir était près de la fenêtre.
+narrateur|Il a joué aux balançoires.
+narrateur|Il a pris le doudou.
+narrateur|Puis il a préparé le sac.
+papa|Il a repris ses affaires.
+papa|Avant de partir.
+maman|Bravo, Amir.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai le seau.
+enfant-m|J'ai le manteau.
+narrateur|Le carré de soleil est vide, maintenant.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16054,7 +16887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16981,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-020.xlsx
+++ b/stories/arbres/TREE-AUT-020.xlsx
@@ -1980,17 +1980,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amir se baisse vers le coussin. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide.</t>
+          <t>Amir se baisse vers le coussin rayé. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir se baisse vers le coussin. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir se baisse vers le &lt;emphasis level="moderate"&gt;coussin rayé&lt;/emphasis&gt;. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Amir se baisse vers le coussin. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide. [pause]</t>
+          <t>Amir se baisse vers le &lt;emphasis&gt;coussin rayé&lt;/emphasis&gt;. Il le reprend, grain par grain. Je le reprends, il est à moi. Merci, Amir. Tu le portes, sans courir ? Oui, je reste. Un grain orange reste sur le tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le bac garde un creux, vide. [pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>reprendre</t>
+          <t>coussin rayé</t>
         </is>
       </c>
       <c r="AI6" s="2" t="n">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Amir se baisse vers le coussin.
+          <t>narrateur|Amir se baisse vers le coussin rayé.
 narrateur|Il le reprend, grain par grain.
 enfant-m|Je le reprends, il est à moi.
 papa|Merci, Amir.
@@ -2951,17 +2951,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau de pollen dort sur la manche.</t>
+          <t>Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau de pollen dort sur la manche.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt; dort sur la manche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen dort sur la manche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt; dort sur la manche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le rebord chaud porte le chat, enfin. Le coussin rayé a un grain de sable. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen dort sur la manche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau de pollen dort sur la manche.</t>
         </is>
@@ -3335,17 +3335,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau de pollen dore le lacet, minuscule.</t>
+          <t>Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau de pollen dore le lacet, minuscule.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt; dore le lacet, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen dore le lacet, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt; dore le lacet, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Voilà le chat, près des chaussures brunes. Le coussin rayé a un grain, et un lacet. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen dore le lacet, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
 narrateur|Le ballon dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau de pollen dore le lacet, minuscule.</t>
         </is>
@@ -3719,17 +3719,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau de pollen brille sur la sangle.</t>
+          <t>Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau de pollen brille sur la sangle.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt; brille sur la sangle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen brille sur la sangle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt; brille sur la sangle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Contre le sac, le chat se fait petit. Le coussin rayé a un grain, près du rabat. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau de pollen brille sur la sangle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau de pollen brille sur la sangle.</t>
         </is>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.</t>
+          <t>Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au chaud, le chat a choisi le nid. Le coussin rayé sent le seau, et le col. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange reste au col, secret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4589,7 +4589,11 @@
       <c r="AG19" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI19" s="2" t="n">
         <v>0</v>
       </c>
@@ -4648,7 +4652,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un cercle orange reste au col, secret.</t>
         </is>
@@ -4876,17 +4880,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.</t>
+          <t>Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Près du seau, le chat ferme un œil. Le coussin rayé sent le seau, et le cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange dort dans le cuir.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4969,7 +4973,11 @@
       <c r="AG21" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI21" s="2" t="n">
         <v>0</v>
       </c>
@@ -5028,7 +5036,7 @@
 narrateur|Le seau dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un cercle orange dort dans le cuir.</t>
         </is>
@@ -5256,17 +5264,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.</t>
+          <t>Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sous le rabat, un museau gris paraît. Le coussin rayé sent le seau, et le sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un cercle orange veille sur le rabat.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5349,7 +5357,11 @@
       <c r="AG23" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI23" s="2" t="n">
         <v>0</v>
       </c>
@@ -5408,7 +5420,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un cercle orange veille sur le rabat.</t>
         </is>
@@ -6029,17 +6041,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.</t>
+          <t>Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou veille, le chat est au nid. Le coussin rayé a l'oreille grise, collée. Il est venu, presque pas. Le jardin des trois coins se tait. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre à la manche.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6122,7 +6134,11 @@
       <c r="AG27" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI27" s="2" t="n">
         <v>0</v>
       </c>
@@ -6181,7 +6197,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voilà le pollen, parti du verre à la manche.</t>
         </is>
@@ -6409,17 +6425,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.</t>
+          <t>L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille grise pend, près des souliers. Le coussin rayé a l'oreille, près du cuir. J'ai attendu, et il est venu. Le jardin des trois coins se tait. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6502,7 +6518,11 @@
       <c r="AG29" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI29" s="2" t="n">
         <v>0</v>
       </c>
@@ -6561,7 +6581,7 @@
 narrateur|Le doudou dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voilà le pollen, parti du verre au lacet.</t>
         </is>
@@ -6789,17 +6809,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.</t>
+          <t>Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Dans le sac, le chat se tait. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. Le jardin des trois coins se tait. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voilà le pollen, parti du verre au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6882,7 +6902,11 @@
       <c r="AG31" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI31" s="2" t="n">
         <v>0</v>
       </c>
@@ -6941,7 +6965,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voilà le pollen, parti du verre au sac.</t>
         </is>
@@ -7355,17 +7379,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Amir ramasse le coussin, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant.</t>
+          <t>Amir ramasse le coussin rayé, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir ramasse le coussin, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir ramasse le &lt;emphasis level="moderate"&gt;coussin rayé&lt;/emphasis&gt;, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Amir ramasse le coussin, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant. [pause]</t>
+          <t>Amir ramasse le &lt;emphasis&gt;coussin rayé&lt;/emphasis&gt;, au bas. Il le reprend, contre lui. Je le reprends, il est froid. Bravo, Amir. Tu le portes, sans glisser ? Oui, je marche. Une feuille reste collée au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. Le métal se tait, un instant. [pause]</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -7446,7 +7470,7 @@
       </c>
       <c r="AH34" s="2" t="inlineStr">
         <is>
-          <t>reprendre</t>
+          <t>coussin rayé</t>
         </is>
       </c>
       <c r="AI34" s="2" t="n">
@@ -7499,7 +7523,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Amir ramasse le coussin, au bas.
+          <t>narrateur|Amir ramasse le coussin rayé, au bas.
 narrateur|Il le reprend, contre lui.
 enfant-m|Je le reprends, il est froid.
 maman|Bravo, Amir.
@@ -8326,17 +8350,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.</t>
+          <t>Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Après le métal, le rebord est doux. Le coussin rayé a une feuille de rampe. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au tissu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8419,7 +8443,11 @@
       <c r="AG39" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI39" s="2" t="n">
         <v>0</v>
       </c>
@@ -8478,7 +8506,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau orange a glissé du métal au tissu.</t>
         </is>
@@ -8706,17 +8734,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.</t>
+          <t>Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au bas des marches, le chat s'installe. Le coussin rayé a une feuille, et le lacet. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8799,7 +8827,11 @@
       <c r="AG41" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI41" s="2" t="n">
         <v>0</v>
       </c>
@@ -8858,7 +8890,7 @@
 narrateur|Le ballon dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau orange a glissé du métal au lacet.</t>
         </is>
@@ -9086,17 +9118,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.</t>
+          <t>Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac beige tient un secret gris. Le coussin rayé a une feuille, près du sac. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. L'anneau orange a glissé du métal au sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9179,7 +9211,11 @@
       <c r="AG43" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI43" s="2" t="n">
         <v>0</v>
       </c>
@@ -9238,7 +9274,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|L'anneau orange a glissé du métal au sac.</t>
         </is>
@@ -9859,17 +9895,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.</t>
+          <t>Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau sonne, loin du nid bleu. Le coussin rayé a une goutte, au col. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au col, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9952,7 +9988,11 @@
       <c r="AG47" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI47" s="2" t="n">
         <v>0</v>
       </c>
@@ -10011,7 +10051,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Une poussière orange sèche au col, fine.</t>
         </is>
@@ -10239,17 +10279,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.</t>
+          <t>Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une goutte sèche, près du cuir brun. Le coussin rayé a une goutte, au cuir. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au cuir, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10332,7 +10372,11 @@
       <c r="AG49" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI49" s="2" t="n">
         <v>0</v>
       </c>
@@ -10391,7 +10435,7 @@
 narrateur|Le seau dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Une poussière orange sèche au cuir, fine.</t>
         </is>
@@ -10619,17 +10663,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.</t>
+          <t>Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau cale le sac, le chat dedans. Le coussin rayé a une goutte, au rabat. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Une poussière orange sèche au rabat, fine.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10712,7 +10756,11 @@
       <c r="AG51" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI51" s="2" t="n">
         <v>0</v>
       </c>
@@ -10771,7 +10819,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Une poussière orange sèche au rabat, fine.</t>
         </is>
@@ -11392,17 +11440,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.</t>
+          <t>Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a vu le manteau, puis le chat. Le coussin rayé a le doudou, et le bleu. Il est venu, presque pas. Le métal se tait, lui aussi. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le manteau garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11485,7 +11533,11 @@
       <c r="AG55" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI55" s="2" t="n">
         <v>0</v>
       </c>
@@ -11544,7 +11596,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voici le verre nu, le manteau garde l'anneau.</t>
         </is>
@@ -11772,17 +11824,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.</t>
+          <t>L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille molle touche un lacet, puis se tait. Le coussin rayé a le doudou, et le brun. J'ai attendu, et il est venu. Le métal se tait, lui aussi. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le lacet garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11865,7 +11917,11 @@
       <c r="AG57" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI57" s="2" t="n">
         <v>0</v>
       </c>
@@ -11924,7 +11980,7 @@
 narrateur|Le doudou dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voici le verre nu, le lacet garde l'anneau.</t>
         </is>
@@ -12152,17 +12208,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.</t>
+          <t>Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Près du métal, le sac garde le chat. Le coussin rayé a le doudou, et le beige. Le tic s'est tu, papa. Le métal se tait, lui aussi. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Voici le verre nu, le sac garde l'anneau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12245,7 +12301,11 @@
       <c r="AG59" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI59" s="2" t="n">
         <v>0</v>
       </c>
@@ -12304,7 +12364,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Voici le verre nu, le sac garde l'anneau.</t>
         </is>
@@ -12718,17 +12778,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Amir reprend le coussin, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit.</t>
+          <t>Amir reprend le coussin rayé, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir reprend le coussin, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir reprend le &lt;emphasis level="moderate"&gt;coussin rayé&lt;/emphasis&gt;, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Amir reprend le coussin, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit. [pause]</t>
+          <t>Amir reprend le &lt;emphasis&gt;coussin rayé&lt;/emphasis&gt;, sur le bois. Il le secoue, sans pousser le siège. Je le reprends, il est à moi. Oui, tes mains sont prêtes. Tu le portes, sans balancer ? Oui, je reste. Un brin de corde reste au tissu. Le chat observe, loin, dans l'herbe. J'attends, moi aussi. La corde retombe, sans bruit. [pause]</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -12809,7 +12869,7 @@
       </c>
       <c r="AH62" s="2" t="inlineStr">
         <is>
-          <t>reprendre</t>
+          <t>coussin rayé</t>
         </is>
       </c>
       <c r="AI62" s="2" t="n">
@@ -12862,7 +12922,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Amir reprend le coussin, sur le bois.
+          <t>narrateur|Amir reprend le coussin rayé, sur le bois.
 narrateur|Il le secoue, sans pousser le siège.
 enfant-m|Je le reprends, il est à moi.
 papa|Oui, tes mains sont prêtes.
@@ -13689,17 +13749,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.</t>
+          <t>La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La corde se tait, le chat est rentré. Le coussin rayé a un brin de corde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le ballon dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le bleu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13782,7 +13842,11 @@
       <c r="AG67" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI67" s="2" t="n">
         <v>0</v>
       </c>
@@ -13841,7 +13905,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un tic lointain, puis l'anneau sur le bleu.</t>
         </is>
@@ -14069,17 +14133,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.</t>
+          <t>Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Un cling lointain, et les chaussures, et lui. Le coussin rayé a un brin, près du lacet. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le ballon dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le lacet.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -14162,7 +14226,11 @@
       <c r="AG69" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AH69" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI69" s="2" t="n">
         <v>0</v>
       </c>
@@ -14221,7 +14289,7 @@
 narrateur|Le ballon dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un tic lointain, puis l'anneau sur le lacet.</t>
         </is>
@@ -14449,17 +14517,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.</t>
+          <t>Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le sac beige a cessé de balancer. Le coussin rayé a un brin, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le ballon dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Un tic lointain, puis l'anneau sur le beige.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14542,7 +14610,11 @@
       <c r="AG71" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH71" s="2" t="inlineStr"/>
+      <c r="AH71" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI71" s="2" t="n">
         <v>0</v>
       </c>
@@ -14601,7 +14673,7 @@
 narrateur|Le ballon dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Un tic lointain, puis l'anneau sur le beige.</t>
         </is>
@@ -15222,17 +15294,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.</t>
+          <t>L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'anse froide a laissé le nid tranquille. Le coussin rayé a l'ombre du seau, ronde. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le seau dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au col.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15315,7 +15387,11 @@
       <c r="AG75" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AH75" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI75" s="2" t="n">
         <v>0</v>
       </c>
@@ -15374,7 +15450,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|La corde se tait, l'anneau reste au col.</t>
         </is>
@@ -15602,17 +15678,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.</t>
+          <t>Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le seau pose son ombre, loin des pattes. Le coussin rayé a l'ombre du seau, au cuir. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le seau dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au cuir.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15695,7 +15771,11 @@
       <c r="AG77" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AH77" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI77" s="2" t="n">
         <v>0</v>
       </c>
@@ -15754,7 +15834,7 @@
 narrateur|Le seau dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|La corde se tait, l'anneau reste au cuir.</t>
         </is>
@@ -15982,17 +16062,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.</t>
+          <t>Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Au pied de bois, le sac tient le chat. Le coussin rayé a l'ombre du seau, au rabat. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le seau dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. La corde se tait, l'anneau reste au rabat.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -16075,7 +16155,11 @@
       <c r="AG79" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AH79" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI79" s="2" t="n">
         <v>0</v>
       </c>
@@ -16134,7 +16218,7 @@
 narrateur|Le seau dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|La corde se tait, l'anneau reste au rabat.</t>
         </is>
@@ -16755,17 +16839,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.</t>
+          <t>L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'oreille grise veille, près du col bleu. Le coussin rayé a l'oreille, près du nid. Il est venu, presque pas. La corde se tait, maintenant. Le manteau bleu fait nid, sous lui. Le doudou dort, loin des pattes. On rentre, le manteau avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Sur le nid, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16848,7 +16932,11 @@
       <c r="AG83" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI83" s="2" t="n">
         <v>0</v>
       </c>
@@ -16907,7 +16995,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le manteau avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Sur le nid, l'anneau reste, tout net.</t>
         </is>
@@ -17135,17 +17223,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.</t>
+          <t>Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou chauffe, les chaussures aussi. Le coussin rayé a l'oreille, près des souliers. J'ai attendu, et il est venu. La corde se tait, maintenant. Les chaussures brunes veillent, près de lui. Le doudou dort, loin des pattes. On rentre, les chaussures avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Près des souliers, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -17228,7 +17316,11 @@
       <c r="AG85" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI85" s="2" t="n">
         <v>0</v>
       </c>
@@ -17287,7 +17379,7 @@
 narrateur|Le doudou dort, loin des pattes.
 maman|On rentre, les chaussures avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Près des souliers, l'anneau reste, tout net.</t>
         </is>
@@ -17515,17 +17607,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.</t>
+          <t>Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'anneau de pollen. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis level="moderate"&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin des pattes. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Trois tissus, et le chat au milieu. Le coussin rayé a l'oreille, près du sac. Le tic s'est tu, papa. La corde se tait, maintenant. Le sac beige fait grotte, autour de lui. Le doudou dort, loin des pattes. On rentre, le sac avec nous. Le chat aussi, sur le rebord. Amir pose une main, loin de l'&lt;emphasis&gt;anneau de pollen&lt;/emphasis&gt;. Sa poitrine se desserre, fière, calme. Près du sac, l'anneau reste, tout net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17608,7 +17700,11 @@
       <c r="AG87" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr">
+        <is>
+          <t>anneau de pollen</t>
+        </is>
+      </c>
       <c r="AI87" s="2" t="n">
         <v>0</v>
       </c>
@@ -17667,7 +17763,7 @@
 narrateur|Le doudou dort, loin des pattes.
 papa|On rentre, le sac avec nous.
 enfant-m|Le chat aussi, sur le rebord.
-narrateur|Amir pose une main, loin des pattes.
+narrateur|Amir pose une main, loin de l'anneau de pollen.
 narrateur|Sa poitrine se desserre, fière, calme.
 narrateur|Près du sac, l'anneau reste, tout net.</t>
         </is>
@@ -17695,7 +17791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17808,6 +17904,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
